--- a/MinMax/scripts/comparison/accuracy_comparison_table_118_1000_inference.xlsx
+++ b/MinMax/scripts/comparison/accuracy_comparison_table_118_1000_inference.xlsx
@@ -1,26 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-22.04\home\bagir\Documents\1) Projects\2) AC verification\MinMax\scripts\comparison\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FACA0275-9B06-423B-8682-37AEAC00A661}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="30">
   <si>
     <t>Pg Vm Model False</t>
   </si>
@@ -37,89 +31,86 @@
     <t>Metric [MSE]</t>
   </si>
   <si>
+    <t>Ibr_from_r_tot</t>
+  </si>
+  <si>
+    <t>pd_tot</t>
+  </si>
+  <si>
+    <t>slack_tot</t>
+  </si>
+  <si>
+    <t>pinj_tot</t>
+  </si>
+  <si>
+    <t>qinj_tot</t>
+  </si>
+  <si>
     <t>vi_tot</t>
   </si>
   <si>
+    <t>Iinj_r_tot</t>
+  </si>
+  <si>
+    <t>nn_input</t>
+  </si>
+  <si>
+    <t>Ibr_to_r_tot</t>
+  </si>
+  <si>
+    <t>cost_tot</t>
+  </si>
+  <si>
+    <t>vr_tot</t>
+  </si>
+  <si>
+    <t>Ibr_from_i_tot</t>
+  </si>
+  <si>
+    <t>pg_tot</t>
+  </si>
+  <si>
+    <t>qg_tot</t>
+  </si>
+  <si>
+    <t>vm_tot</t>
+  </si>
+  <si>
     <t>Ibr_to_i_tot</t>
   </si>
   <si>
+    <t>qd_tot</t>
+  </si>
+  <si>
     <t>Iinj_i_tot</t>
   </si>
   <si>
-    <t>vr_tot</t>
-  </si>
-  <si>
-    <t>Ibr_from_r_tot</t>
-  </si>
-  <si>
-    <t>Ibr_to_r_tot</t>
-  </si>
-  <si>
-    <t>qd_tot</t>
-  </si>
-  <si>
-    <t>qg_tot</t>
-  </si>
-  <si>
-    <t>nn_input</t>
-  </si>
-  <si>
-    <t>vm_tot</t>
-  </si>
-  <si>
-    <t>Ibr_from_i_tot</t>
-  </si>
-  <si>
-    <t>Iinj_r_tot</t>
-  </si>
-  <si>
-    <t>qinj_tot</t>
-  </si>
-  <si>
-    <t>slack_tot</t>
-  </si>
-  <si>
-    <t>pd_tot</t>
-  </si>
-  <si>
-    <t>pg_tot</t>
-  </si>
-  <si>
-    <t>cost_tot</t>
-  </si>
-  <si>
-    <t>pinj_tot</t>
-  </si>
-  <si>
-    <t>1.09 (1.96)</t>
-  </si>
-  <si>
-    <t>67579.50 (69774.76 &gt; 3.14%)</t>
-  </si>
-  <si>
-    <t>1.10 (1.96)</t>
-  </si>
-  <si>
-    <t>67584.98 (69774.76 &gt; 3.13%)</t>
-  </si>
-  <si>
-    <t>-0.84 (1.96)</t>
-  </si>
-  <si>
-    <t>69938.71 (69774.76 &gt; 1.22%)</t>
-  </si>
-  <si>
-    <t>-0.80 (1.96)</t>
-  </si>
-  <si>
-    <t>69283.80 (69774.76 &gt; 1.23%)</t>
+    <t>1.11 (1.97)</t>
+  </si>
+  <si>
+    <t>67852.20 (70058.73 &gt; 3.14%)</t>
+  </si>
+  <si>
+    <t>67856.79 (70058.73 &gt; 3.14%)</t>
+  </si>
+  <si>
+    <t>-0.84 (1.97)</t>
+  </si>
+  <si>
+    <t>70205.17 (70058.73 &gt; 1.26%)</t>
+  </si>
+  <si>
+    <t>-0.81 (1.97)</t>
+  </si>
+  <si>
+    <t>69543.66 (70058.73 &gt; 1.23%)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -182,21 +173,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -234,7 +217,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -268,7 +251,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -303,10 +285,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -479,15 +460,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E19"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="13.6328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="5" width="24.81640625" bestFit="1" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
@@ -504,310 +481,310 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B2">
-        <v>0.68057781457901001</v>
+        <v>3.080591404428186</v>
       </c>
       <c r="C2">
-        <v>0.68057906627655029</v>
+        <v>3.08060159097479</v>
       </c>
       <c r="D2">
-        <v>2.0273754489608109E-4</v>
+        <v>0.03055061399936676</v>
       </c>
       <c r="E2">
-        <v>4.9649842549115419E-4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+        <v>0.02712614275515079</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B3">
-        <v>1.067285021761579</v>
+        <v>0</v>
       </c>
       <c r="C3">
-        <v>1.0672886169195841</v>
+        <v>0</v>
       </c>
       <c r="D3">
-        <v>3.3435013145208359E-2</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>3.7293825298547738E-2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
       <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B4">
-        <v>1.060041267203738</v>
-      </c>
-      <c r="C4">
-        <v>1.060047277550018</v>
-      </c>
-      <c r="D4">
-        <v>0.1104749068617821</v>
-      </c>
-      <c r="E4">
-        <v>0.12263529002666471</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B5">
-        <v>0.58665943145751953</v>
+        <v>9.514405250549316</v>
       </c>
       <c r="C5">
-        <v>0.58666175603866577</v>
+        <v>9.514442443847656</v>
       </c>
       <c r="D5">
-        <v>3.9544211176689707E-5</v>
+        <v>0.1027604788541794</v>
       </c>
       <c r="E5">
-        <v>3.1606422271579499E-4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+        <v>0.09665176272392273</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
       <c r="A6" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B6">
-        <v>3.0787979046624621</v>
+        <v>1.188111782073975</v>
       </c>
       <c r="C6">
-        <v>3.0788077861577401</v>
+        <v>1.188119173049927</v>
       </c>
       <c r="D6">
-        <v>3.0715439468622211E-2</v>
+        <v>0.1110167801380157</v>
       </c>
       <c r="E6">
-        <v>2.7306105941534039E-2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+        <v>0.1215375736355782</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
       <c r="A7" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B7">
-        <v>2.8720634567295931</v>
+        <v>0.6799859404563904</v>
       </c>
       <c r="C7">
-        <v>2.872072558294116</v>
+        <v>0.679987907409668</v>
       </c>
       <c r="D7">
-        <v>2.9001714661717411E-2</v>
+        <v>0.0002117378462571651</v>
       </c>
       <c r="E7">
-        <v>2.5670303031802181E-2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+        <v>0.0004786221543326974</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
       <c r="A8" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B8">
-        <v>0</v>
+        <v>10.00926702867042</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>10.00930644821902</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>0.1004981026053429</v>
       </c>
       <c r="E8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+        <v>0.09222771227359772</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
       <c r="A9" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B9">
-        <v>0.1248921751976013</v>
+        <v>0</v>
       </c>
       <c r="C9">
-        <v>0.1248921751976013</v>
+        <v>0</v>
       </c>
       <c r="D9">
-        <v>8.1613361835479736E-2</v>
+        <v>0</v>
       </c>
       <c r="E9">
-        <v>0.1098262146115303</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
       <c r="A10" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B10">
-        <v>7.4556116504896397E-17</v>
+        <v>2.872817804108746</v>
       </c>
       <c r="C10">
-        <v>7.4556116504896397E-17</v>
+        <v>2.872827194049673</v>
       </c>
       <c r="D10">
-        <v>7.4556116504896397E-17</v>
+        <v>0.02885441295802593</v>
       </c>
       <c r="E10">
-        <v>7.4556116504896397E-17</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+        <v>0.02550480328500271</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
       <c r="A11" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B11">
-        <v>2.389557426795363E-3</v>
-      </c>
-      <c r="C11">
-        <v>2.389558125287294E-3</v>
-      </c>
-      <c r="D11">
-        <v>3.765006476896815E-5</v>
-      </c>
-      <c r="E11">
-        <v>3.1462172046303749E-4</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B11" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" t="s">
+        <v>25</v>
+      </c>
+      <c r="D11" t="s">
+        <v>27</v>
+      </c>
+      <c r="E11" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
       <c r="A12" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B12">
-        <v>1.0166547417225911</v>
+        <v>0.5865538120269775</v>
       </c>
       <c r="C12">
-        <v>1.016658114120188</v>
+        <v>0.5865572690963745</v>
       </c>
       <c r="D12">
-        <v>3.4959778189659119E-2</v>
+        <v>4.108626308152452E-05</v>
       </c>
       <c r="E12">
-        <v>3.8977969437837601E-2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+        <v>0.0003228076966479421</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
       <c r="A13" s="1" t="s">
         <v>16</v>
       </c>
       <c r="B13">
-        <v>10.015802495877351</v>
+        <v>1.016641530594742</v>
       </c>
       <c r="C13">
-        <v>10.015847392573191</v>
+        <v>1.016646001888152</v>
       </c>
       <c r="D13">
-        <v>0.1013282537460327</v>
+        <v>0.03481541946530342</v>
       </c>
       <c r="E13">
-        <v>9.3182764947414398E-2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+        <v>0.03865188732743263</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
       <c r="A14" s="1" t="s">
         <v>17</v>
       </c>
       <c r="B14">
-        <v>1.1884529590606689</v>
+        <v>0.0004452389811292131</v>
       </c>
       <c r="C14">
-        <v>1.1884605884552</v>
+        <v>0.0008329581131642929</v>
       </c>
       <c r="D14">
-        <v>0.1111196205019951</v>
+        <v>0.1119898855686188</v>
       </c>
       <c r="E14">
-        <v>0.1218371018767357</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+        <v>0.1012229323387146</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
       <c r="A15" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B15" t="s">
-        <v>23</v>
-      </c>
-      <c r="C15" t="s">
-        <v>25</v>
-      </c>
-      <c r="D15" t="s">
-        <v>27</v>
-      </c>
-      <c r="E15" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B15">
+        <v>0.1246090605854988</v>
+      </c>
+      <c r="C15">
+        <v>0.1246090605854988</v>
+      </c>
+      <c r="D15">
+        <v>0.08083400130271912</v>
+      </c>
+      <c r="E15">
+        <v>0.108713299036026</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
       <c r="A16" s="1" t="s">
         <v>19</v>
       </c>
       <c r="B16">
-        <v>0</v>
+        <v>0.002387456828728318</v>
       </c>
       <c r="C16">
-        <v>0</v>
+        <v>0.002387459389865398</v>
       </c>
       <c r="D16">
-        <v>0</v>
+        <v>3.844668390229344E-05</v>
       </c>
       <c r="E16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+        <v>0.0003195261233486235</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
       <c r="A17" s="1" t="s">
         <v>20</v>
       </c>
       <c r="B17">
-        <v>3.9470773023806029E-4</v>
+        <v>1.06756667602413</v>
       </c>
       <c r="C17">
-        <v>7.7183819618481184E-4</v>
+        <v>1.067571435576963</v>
       </c>
       <c r="D17">
-        <v>0.11069326102733611</v>
+        <v>0.03329214826226234</v>
       </c>
       <c r="E17">
-        <v>9.9711418151855469E-2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+        <v>0.03698097169399261</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
       <c r="A18" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B18" t="s">
-        <v>24</v>
-      </c>
-      <c r="C18" t="s">
-        <v>26</v>
-      </c>
-      <c r="D18" t="s">
-        <v>28</v>
-      </c>
-      <c r="E18" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B18">
+        <v>0</v>
+      </c>
+      <c r="C18">
+        <v>0</v>
+      </c>
+      <c r="D18">
+        <v>0</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
       <c r="A19" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B19">
-        <v>9.519587516784668</v>
+        <v>1.06087289515166</v>
       </c>
       <c r="C19">
-        <v>9.5196294784545898</v>
+        <v>1.060880683517419</v>
       </c>
       <c r="D19">
-        <v>0.10350727289915081</v>
+        <v>0.1104201227426529</v>
       </c>
       <c r="E19">
-        <v>9.7437828779220581E-2</v>
+        <v>0.1222375333309174</v>
       </c>
     </row>
   </sheetData>

--- a/MinMax/scripts/comparison/accuracy_comparison_table_118_1000_inference.xlsx
+++ b/MinMax/scripts/comparison/accuracy_comparison_table_118_1000_inference.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
   <si>
     <t>Pg Vm Model False</t>
   </si>
@@ -31,79 +31,85 @@
     <t>Metric [MSE]</t>
   </si>
   <si>
+    <t>pg_tot</t>
+  </si>
+  <si>
+    <t>sample_num</t>
+  </si>
+  <si>
+    <t>pinj_tot</t>
+  </si>
+  <si>
+    <t>qinj_tot</t>
+  </si>
+  <si>
+    <t>vr_tot</t>
+  </si>
+  <si>
+    <t>cost_tot</t>
+  </si>
+  <si>
     <t>Ibr_from_r_tot</t>
   </si>
   <si>
+    <t>Ibr_from_i_tot</t>
+  </si>
+  <si>
+    <t>vi_tot</t>
+  </si>
+  <si>
+    <t>nn_input</t>
+  </si>
+  <si>
+    <t>Iinj_r_tot</t>
+  </si>
+  <si>
+    <t>Ibr_to_r_tot</t>
+  </si>
+  <si>
+    <t>qg_tot</t>
+  </si>
+  <si>
+    <t>Ibr_to_i_tot</t>
+  </si>
+  <si>
     <t>pd_tot</t>
   </si>
   <si>
+    <t>qd_tot</t>
+  </si>
+  <si>
     <t>slack_tot</t>
   </si>
   <si>
-    <t>pinj_tot</t>
-  </si>
-  <si>
-    <t>qinj_tot</t>
-  </si>
-  <si>
-    <t>vi_tot</t>
-  </si>
-  <si>
-    <t>Iinj_r_tot</t>
-  </si>
-  <si>
-    <t>nn_input</t>
-  </si>
-  <si>
-    <t>Ibr_to_r_tot</t>
-  </si>
-  <si>
-    <t>cost_tot</t>
-  </si>
-  <si>
-    <t>vr_tot</t>
-  </si>
-  <si>
-    <t>Ibr_from_i_tot</t>
-  </si>
-  <si>
-    <t>pg_tot</t>
-  </si>
-  <si>
-    <t>qg_tot</t>
+    <t>Iinj_i_tot</t>
   </si>
   <si>
     <t>vm_tot</t>
   </si>
   <si>
-    <t>Ibr_to_i_tot</t>
-  </si>
-  <si>
-    <t>qd_tot</t>
-  </si>
-  <si>
-    <t>Iinj_i_tot</t>
-  </si>
-  <si>
-    <t>1.11 (1.97)</t>
-  </si>
-  <si>
-    <t>67852.20 (70058.73 &gt; 3.14%)</t>
-  </si>
-  <si>
-    <t>67856.79 (70058.73 &gt; 3.14%)</t>
-  </si>
-  <si>
-    <t>-0.84 (1.97)</t>
-  </si>
-  <si>
-    <t>70205.17 (70058.73 &gt; 1.26%)</t>
-  </si>
-  <si>
-    <t>-0.81 (1.97)</t>
-  </si>
-  <si>
-    <t>69543.66 (70058.73 &gt; 1.23%)</t>
+    <t>67890.32 (70058.73 &gt; 3.10%)</t>
+  </si>
+  <si>
+    <t>1.14 (196.99)</t>
+  </si>
+  <si>
+    <t>67877.40 (70058.73 &gt; 3.11%)</t>
+  </si>
+  <si>
+    <t>1.13 (196.99)</t>
+  </si>
+  <si>
+    <t>70205.17 (70058.73 &gt; 0.21%)</t>
+  </si>
+  <si>
+    <t>-0.84 (196.99)</t>
+  </si>
+  <si>
+    <t>69543.66 (70058.73 &gt; 0.74%)</t>
+  </si>
+  <si>
+    <t>-0.81 (196.99)</t>
   </si>
 </sst>
 </file>
@@ -461,7 +467,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -486,50 +492,38 @@
         <v>5</v>
       </c>
       <c r="B2">
-        <v>3.080591404428186</v>
+        <v>0.0003971460745186948</v>
       </c>
       <c r="C2">
-        <v>3.08060159097479</v>
+        <v>0.000780420686318238</v>
       </c>
       <c r="D2">
-        <v>0.03055061399936676</v>
+        <v>0.1119898781180382</v>
       </c>
       <c r="E2">
-        <v>0.02712614275515079</v>
+        <v>0.1012229323387146</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B3">
-        <v>0</v>
-      </c>
-      <c r="C3">
-        <v>0</v>
-      </c>
-      <c r="D3">
-        <v>0</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E4" t="s">
-        <v>28</v>
+      <c r="B4">
+        <v>9.514681816101074</v>
+      </c>
+      <c r="C4">
+        <v>9.514582633972168</v>
+      </c>
+      <c r="D4">
+        <v>0.10276048630476</v>
+      </c>
+      <c r="E4">
+        <v>0.09665176272392273</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -537,16 +531,16 @@
         <v>8</v>
       </c>
       <c r="B5">
-        <v>9.514405250549316</v>
+        <v>1.188189506530762</v>
       </c>
       <c r="C5">
-        <v>9.514442443847656</v>
+        <v>1.188158869743347</v>
       </c>
       <c r="D5">
-        <v>0.1027604788541794</v>
+        <v>0.1110168024897575</v>
       </c>
       <c r="E5">
-        <v>0.09665176272392273</v>
+        <v>0.1215375810861588</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -554,33 +548,33 @@
         <v>9</v>
       </c>
       <c r="B6">
-        <v>1.188111782073975</v>
+        <v>0.5865848064422607</v>
       </c>
       <c r="C6">
-        <v>1.188119173049927</v>
+        <v>0.5865742564201355</v>
       </c>
       <c r="D6">
-        <v>0.1110167801380157</v>
+        <v>4.108626671950333E-05</v>
       </c>
       <c r="E6">
-        <v>0.1215375736355782</v>
+        <v>0.0003228076675441116</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B7">
-        <v>0.6799859404563904</v>
-      </c>
-      <c r="C7">
-        <v>0.679987907409668</v>
-      </c>
-      <c r="D7">
-        <v>0.0002117378462571651</v>
-      </c>
-      <c r="E7">
-        <v>0.0004786221543326974</v>
+      <c r="B7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" t="s">
+        <v>28</v>
+      </c>
+      <c r="E7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -588,16 +582,16 @@
         <v>11</v>
       </c>
       <c r="B8">
-        <v>10.00926702867042</v>
+        <v>3.080659162924187</v>
       </c>
       <c r="C8">
-        <v>10.00930644821902</v>
+        <v>3.080633988381485</v>
       </c>
       <c r="D8">
-        <v>0.1004981026053429</v>
+        <v>0.03055061399936676</v>
       </c>
       <c r="E8">
-        <v>0.09222771227359772</v>
+        <v>0.02712614275515079</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -605,16 +599,16 @@
         <v>12</v>
       </c>
       <c r="B9">
-        <v>0</v>
+        <v>1.016695208310304</v>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>1.016674011192768</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>0.03481541946530342</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>0.03865188360214233</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -622,33 +616,33 @@
         <v>13</v>
       </c>
       <c r="B10">
-        <v>2.872817804108746</v>
+        <v>0.6799913644790649</v>
       </c>
       <c r="C10">
-        <v>2.872827194049673</v>
+        <v>0.6799905896186829</v>
       </c>
       <c r="D10">
-        <v>0.02885441295802593</v>
+        <v>0.0002117378462571651</v>
       </c>
       <c r="E10">
-        <v>0.02550480328500271</v>
+        <v>0.0004786221543326974</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B11" t="s">
-        <v>24</v>
-      </c>
-      <c r="C11" t="s">
-        <v>25</v>
-      </c>
-      <c r="D11" t="s">
-        <v>27</v>
-      </c>
-      <c r="E11" t="s">
-        <v>29</v>
+      <c r="B11">
+        <v>0</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -656,16 +650,16 @@
         <v>15</v>
       </c>
       <c r="B12">
-        <v>0.5865538120269775</v>
+        <v>10.00958204054644</v>
       </c>
       <c r="C12">
-        <v>0.5865572690963745</v>
+        <v>10.00946761326581</v>
       </c>
       <c r="D12">
-        <v>4.108626308152452E-05</v>
+        <v>0.1004981026053429</v>
       </c>
       <c r="E12">
-        <v>0.0003228076966479421</v>
+        <v>0.09222771972417831</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -673,16 +667,16 @@
         <v>16</v>
       </c>
       <c r="B13">
-        <v>1.016641530594742</v>
+        <v>2.87288194708493</v>
       </c>
       <c r="C13">
-        <v>1.016646001888152</v>
+        <v>2.872857674277836</v>
       </c>
       <c r="D13">
-        <v>0.03481541946530342</v>
+        <v>0.02885441668331623</v>
       </c>
       <c r="E13">
-        <v>0.03865188732743263</v>
+        <v>0.02550480142235756</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -690,16 +684,16 @@
         <v>17</v>
       </c>
       <c r="B14">
-        <v>0.0004452389811292131</v>
+        <v>0.1246090605854988</v>
       </c>
       <c r="C14">
-        <v>0.0008329581131642929</v>
+        <v>0.1246090605854988</v>
       </c>
       <c r="D14">
-        <v>0.1119898855686188</v>
+        <v>0.08083398640155792</v>
       </c>
       <c r="E14">
-        <v>0.1012229323387146</v>
+        <v>0.1087132841348648</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -707,16 +701,16 @@
         <v>18</v>
       </c>
       <c r="B15">
-        <v>0.1246090605854988</v>
+        <v>1.067624073030461</v>
       </c>
       <c r="C15">
-        <v>0.1246090605854988</v>
+        <v>1.067601463447605</v>
       </c>
       <c r="D15">
-        <v>0.08083400130271912</v>
+        <v>0.03329214453697205</v>
       </c>
       <c r="E15">
-        <v>0.108713299036026</v>
+        <v>0.03698097169399261</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -724,16 +718,16 @@
         <v>19</v>
       </c>
       <c r="B16">
-        <v>0.002387456828728318</v>
+        <v>0</v>
       </c>
       <c r="C16">
-        <v>0.002387459389865398</v>
+        <v>0</v>
       </c>
       <c r="D16">
-        <v>3.844668390229344E-05</v>
+        <v>0</v>
       </c>
       <c r="E16">
-        <v>0.0003195261233486235</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -741,33 +735,33 @@
         <v>20</v>
       </c>
       <c r="B17">
-        <v>1.06756667602413</v>
+        <v>0</v>
       </c>
       <c r="C17">
-        <v>1.067571435576963</v>
+        <v>0</v>
       </c>
       <c r="D17">
-        <v>0.03329214826226234</v>
+        <v>0</v>
       </c>
       <c r="E17">
-        <v>0.03698097169399261</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B18">
-        <v>0</v>
-      </c>
-      <c r="C18">
-        <v>0</v>
-      </c>
-      <c r="D18">
-        <v>0</v>
-      </c>
-      <c r="E18">
-        <v>0</v>
+      <c r="B18" t="s">
+        <v>25</v>
+      </c>
+      <c r="C18" t="s">
+        <v>27</v>
+      </c>
+      <c r="D18" t="s">
+        <v>29</v>
+      </c>
+      <c r="E18" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -775,16 +769,33 @@
         <v>22</v>
       </c>
       <c r="B19">
-        <v>1.06087289515166</v>
+        <v>1.060926540516621</v>
       </c>
       <c r="C19">
-        <v>1.060880683517419</v>
+        <v>1.060909117939782</v>
       </c>
       <c r="D19">
         <v>0.1104201227426529</v>
       </c>
       <c r="E19">
-        <v>0.1222375333309174</v>
+        <v>0.1222375258803368</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B20">
+        <v>0.002387469634413719</v>
+      </c>
+      <c r="C20">
+        <v>0.002387466840445995</v>
+      </c>
+      <c r="D20">
+        <v>3.844668754027225E-05</v>
+      </c>
+      <c r="E20">
+        <v>0.0003195261233486235</v>
       </c>
     </row>
   </sheetData>
